--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>639.74</v>
+        <v>547.5700000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>545.54</v>
+        <v>519.27</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>412.78</v>
       </c>
       <c r="G2">
-        <v>271.2</v>
+        <v>187.2</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>733.95</v>
       </c>
       <c r="I2">
-        <v>24356</v>
+        <v>17639</v>
       </c>
       <c r="J2">
-        <v>3.495615180277424</v>
+        <v>3.909815396849289</v>
       </c>
       <c r="K2">
-        <v>632.8883796397675</v>
+        <v>539.9063767391459</v>
       </c>
       <c r="L2">
-        <v>646.5916203602325</v>
+        <v>555.2336232608542</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>449.3</v>
+        <v>371.63</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>6202.5</v>
       </c>
       <c r="E3">
-        <v>499.03</v>
+        <v>474.11</v>
       </c>
       <c r="F3">
-        <v>317.14</v>
+        <v>225.59</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="I3">
-        <v>24356</v>
+        <v>17639</v>
       </c>
       <c r="J3">
-        <v>3.197596589459697</v>
+        <v>3.569785617887066</v>
       </c>
       <c r="K3">
-        <v>443.0325143740756</v>
+        <v>364.6328685959066</v>
       </c>
       <c r="L3">
-        <v>455.5674856259244</v>
+        <v>378.6271314040934</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>629.8099999999999</v>
+        <v>532.65</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>547.03</v>
+        <v>519.85</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>385.73</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>715.16</v>
       </c>
       <c r="I2">
-        <v>24740</v>
+        <v>18133</v>
       </c>
       <c r="J2">
-        <v>3.47785360230448</v>
+        <v>3.860496984295292</v>
       </c>
       <c r="K2">
-        <v>622.9931986817376</v>
+        <v>525.0830598332608</v>
       </c>
       <c r="L2">
-        <v>636.6268013182623</v>
+        <v>540.2169401667392</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>442.32</v>
+        <v>361.51</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,28 +617,28 @@
         <v>6202.5</v>
       </c>
       <c r="E3">
-        <v>498.25</v>
+        <v>471.5</v>
       </c>
       <c r="F3">
-        <v>309.43</v>
+        <v>210</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="I3">
-        <v>24740</v>
+        <v>18133</v>
       </c>
       <c r="J3">
-        <v>3.167724909690889</v>
+        <v>3.50144143136526</v>
       </c>
       <c r="K3">
-        <v>436.1110694901116</v>
+        <v>354.6468427649947</v>
       </c>
       <c r="L3">
-        <v>448.5289305098884</v>
+        <v>368.3731572350053</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>547.5700000000001</v>
+        <v>517.2</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>519.27</v>
+        <v>512.78</v>
       </c>
       <c r="F2">
-        <v>412.78</v>
+        <v>374.39</v>
       </c>
       <c r="G2">
-        <v>187.2</v>
+        <v>168</v>
       </c>
       <c r="H2">
-        <v>733.95</v>
+        <v>699.5700000000001</v>
       </c>
       <c r="I2">
-        <v>17639</v>
+        <v>17311</v>
       </c>
       <c r="J2">
-        <v>3.909815396849289</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>539.9063767391459</v>
+        <v>509.56</v>
       </c>
       <c r="L2">
-        <v>555.2336232608542</v>
+        <v>524.84</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>371.63</v>
+        <v>280.67</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6202.5</v>
+        <v>6200</v>
       </c>
       <c r="E3">
-        <v>474.11</v>
+        <v>443.73</v>
       </c>
       <c r="F3">
-        <v>225.59</v>
+        <v>84</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>546</v>
+        <v>420</v>
       </c>
       <c r="I3">
-        <v>17639</v>
+        <v>17311</v>
       </c>
       <c r="J3">
-        <v>3.569785617887066</v>
+        <v>3.37</v>
       </c>
       <c r="K3">
-        <v>364.6328685959066</v>
+        <v>274.06</v>
       </c>
       <c r="L3">
-        <v>378.6271314040934</v>
+        <v>287.28</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>532.65</v>
+        <v>493.76</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>519.85</v>
+        <v>512.4400000000001</v>
       </c>
       <c r="F2">
-        <v>385.73</v>
+        <v>339.77</v>
       </c>
       <c r="G2">
-        <v>168</v>
+        <v>133.38</v>
       </c>
       <c r="H2">
-        <v>715.16</v>
+        <v>672</v>
       </c>
       <c r="I2">
         <v>18133</v>
       </c>
       <c r="J2">
-        <v>3.860496984295292</v>
+        <v>3.81</v>
       </c>
       <c r="K2">
-        <v>525.0830598332608</v>
+        <v>486.3</v>
       </c>
       <c r="L2">
-        <v>540.2169401667392</v>
+        <v>501.22</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>361.51</v>
+        <v>267.95</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6202.5</v>
+        <v>6200</v>
       </c>
       <c r="E3">
-        <v>471.5</v>
+        <v>437.47</v>
       </c>
       <c r="F3">
-        <v>210</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>546</v>
+        <v>397.2</v>
       </c>
       <c r="I3">
         <v>18133</v>
       </c>
       <c r="J3">
-        <v>3.50144143136526</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>354.6468427649947</v>
+        <v>261.58</v>
       </c>
       <c r="L3">
-        <v>368.3731572350053</v>
+        <v>274.32</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>517.2</v>
+        <v>562.1900000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8453.309999999999</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>512.78</v>
+        <v>518.9</v>
       </c>
       <c r="F2">
-        <v>374.39</v>
+        <v>420</v>
       </c>
       <c r="G2">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="H2">
-        <v>699.5700000000001</v>
+        <v>752.39</v>
       </c>
       <c r="I2">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="K2">
-        <v>509.56</v>
+        <v>555.4</v>
       </c>
       <c r="L2">
-        <v>524.84</v>
+        <v>568.98</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>280.67</v>
+        <v>296.69</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>6200</v>
       </c>
       <c r="E3">
-        <v>443.73</v>
+        <v>449.7</v>
       </c>
       <c r="F3">
-        <v>84</v>
+        <v>103.2</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>420</v>
+        <v>439.2</v>
       </c>
       <c r="I3">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J3">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>274.06</v>
+        <v>290.8</v>
       </c>
       <c r="L3">
-        <v>287.28</v>
+        <v>302.58</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>493.76</v>
+        <v>545.1900000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8453.309999999999</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>512.4400000000001</v>
+        <v>519.98</v>
       </c>
       <c r="F2">
-        <v>339.77</v>
+        <v>412.13</v>
       </c>
       <c r="G2">
-        <v>133.38</v>
+        <v>202.78</v>
       </c>
       <c r="H2">
-        <v>672</v>
+        <v>732.7</v>
       </c>
       <c r="I2">
-        <v>18133</v>
+        <v>23106</v>
       </c>
       <c r="J2">
-        <v>3.81</v>
+        <v>3.42</v>
       </c>
       <c r="K2">
-        <v>486.3</v>
+        <v>538.48</v>
       </c>
       <c r="L2">
-        <v>501.22</v>
+        <v>551.89</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>267.95</v>
+        <v>287.71</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,28 +617,28 @@
         <v>6200</v>
       </c>
       <c r="E3">
-        <v>437.47</v>
+        <v>445.75</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>397.2</v>
+        <v>420</v>
       </c>
       <c r="I3">
-        <v>18133</v>
+        <v>23106</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="K3">
-        <v>261.58</v>
+        <v>281.96</v>
       </c>
       <c r="L3">
-        <v>274.32</v>
+        <v>293.46</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>562.1900000000001</v>
+        <v>717.25</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>13571.11</v>
       </c>
       <c r="E2">
-        <v>518.9</v>
+        <v>715.22</v>
       </c>
       <c r="F2">
-        <v>420</v>
+        <v>522.55</v>
       </c>
       <c r="G2">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>752.39</v>
+        <v>950.58</v>
       </c>
       <c r="I2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J2">
-        <v>3.47</v>
+        <v>4.77</v>
       </c>
       <c r="K2">
-        <v>555.4</v>
+        <v>707.9</v>
       </c>
       <c r="L2">
-        <v>568.98</v>
+        <v>726.6</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>296.69</v>
+        <v>384.02</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6200</v>
+        <v>8006</v>
       </c>
       <c r="E3">
-        <v>449.7</v>
+        <v>606.95</v>
       </c>
       <c r="F3">
-        <v>103.2</v>
+        <v>126</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>439.2</v>
+        <v>562.54</v>
       </c>
       <c r="I3">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="K3">
-        <v>290.8</v>
+        <v>376.08</v>
       </c>
       <c r="L3">
-        <v>302.58</v>
+        <v>391.96</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>545.1900000000001</v>
+        <v>721.8200000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>13857.42</v>
       </c>
       <c r="E2">
-        <v>519.98</v>
+        <v>727.09</v>
       </c>
       <c r="F2">
-        <v>412.13</v>
+        <v>526.63</v>
       </c>
       <c r="G2">
-        <v>202.78</v>
+        <v>247.37</v>
       </c>
       <c r="H2">
-        <v>732.7</v>
+        <v>961.99</v>
       </c>
       <c r="I2">
-        <v>23106</v>
+        <v>23007</v>
       </c>
       <c r="J2">
-        <v>3.42</v>
+        <v>4.79</v>
       </c>
       <c r="K2">
-        <v>538.48</v>
+        <v>712.42</v>
       </c>
       <c r="L2">
-        <v>551.89</v>
+        <v>731.22</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>287.71</v>
+        <v>383.92</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6200</v>
+        <v>8688.879999999999</v>
       </c>
       <c r="E3">
-        <v>445.75</v>
+        <v>614.04</v>
       </c>
       <c r="F3">
-        <v>84</v>
+        <v>103.2</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>420</v>
+        <v>564.34</v>
       </c>
       <c r="I3">
-        <v>23106</v>
+        <v>23007</v>
       </c>
       <c r="J3">
-        <v>2.93</v>
+        <v>4.05</v>
       </c>
       <c r="K3">
-        <v>281.96</v>
+        <v>375.99</v>
       </c>
       <c r="L3">
-        <v>293.46</v>
+        <v>391.85</v>
       </c>
     </row>
   </sheetData>
